--- a/reviews/a-envoyer/pierre-huiban-2026-08-17.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-08-17.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T07:09:40</t>
+          <t>2026-08-17T07:32:37</t>
         </is>
       </c>
     </row>
